--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_06-11-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_06-11-2025.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>£9.93</t>
+          <t>£9.83</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>£9.85</t>
+          <t>£9.74</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -592,23 +592,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c97c7a05
-	0x7ff7c97c7a60
-	0x7ff7c95416ad
-	0x7ff7c959a13e
-	0x7ff7c959a44c
-	0x7ff7c95eebe7
-	0x7ff7c95eb8fb
-	0x7ff7c958b068
-	0x7ff7c958be93
-	0x7ff7c9a829a0
-	0x7ff7c9a7ce20
-	0x7ff7c9a9cc15
-	0x7ff7c97e309e
-	0x7ff7c97ead8f
-	0x7ff7c97d0be4
-	0x7ff7c97d0d9f
-	0x7ff7c97b67f8
+	0x7ff6707b7a05
+	0x7ff6707b7a60
+	0x7ff6705316ad
+	0x7ff67058a13e
+	0x7ff67058a44c
+	0x7ff6705debe7
+	0x7ff6705db8fb
+	0x7ff67057b068
+	0x7ff67057be93
+	0x7ff670a729a0
+	0x7ff670a6ce20
+	0x7ff670a8cc15
+	0x7ff6707d309e
+	0x7ff6707dad8f
+	0x7ff6707c0be4
+	0x7ff6707c0d9f
+	0x7ff6707a67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -678,7 +678,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>£11.21</t>
+          <t>£11.10</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -712,23 +712,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c97c7a05
-	0x7ff7c97c7a60
-	0x7ff7c95416ad
-	0x7ff7c959a13e
-	0x7ff7c959a44c
-	0x7ff7c95eebe7
-	0x7ff7c95eb8fb
-	0x7ff7c958b068
-	0x7ff7c958be93
-	0x7ff7c9a829a0
-	0x7ff7c9a7ce20
-	0x7ff7c9a9cc15
-	0x7ff7c97e309e
-	0x7ff7c97ead8f
-	0x7ff7c97d0be4
-	0x7ff7c97d0d9f
-	0x7ff7c97b67f8
+	0x7ff6707b7a05
+	0x7ff6707b7a60
+	0x7ff6705316ad
+	0x7ff67058a13e
+	0x7ff67058a44c
+	0x7ff6705debe7
+	0x7ff6705db8fb
+	0x7ff67057b068
+	0x7ff67057be93
+	0x7ff670a729a0
+	0x7ff670a6ce20
+	0x7ff670a8cc15
+	0x7ff6707d309e
+	0x7ff6707dad8f
+	0x7ff6707c0be4
+	0x7ff6707c0d9f
+	0x7ff6707a67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -798,7 +798,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>£14.50</t>
+          <t>£14.36</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>£14.44</t>
+          <t>£14.04</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -832,23 +832,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c97c7a05
-	0x7ff7c97c7a60
-	0x7ff7c95416ad
-	0x7ff7c959a13e
-	0x7ff7c959a44c
-	0x7ff7c95eebe7
-	0x7ff7c95eb8fb
-	0x7ff7c958b068
-	0x7ff7c958be93
-	0x7ff7c9a829a0
-	0x7ff7c9a7ce20
-	0x7ff7c9a9cc15
-	0x7ff7c97e309e
-	0x7ff7c97ead8f
-	0x7ff7c97d0be4
-	0x7ff7c97d0d9f
-	0x7ff7c97b67f8
+	0x7ff6707b7a05
+	0x7ff6707b7a60
+	0x7ff6705316ad
+	0x7ff67058a13e
+	0x7ff67058a44c
+	0x7ff6705debe7
+	0x7ff6705db8fb
+	0x7ff67057b068
+	0x7ff67057be93
+	0x7ff670a729a0
+	0x7ff670a6ce20
+	0x7ff670a8cc15
+	0x7ff6707d309e
+	0x7ff6707dad8f
+	0x7ff6707c0be4
+	0x7ff6707c0d9f
+	0x7ff6707a67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -918,7 +918,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>£14.78</t>
+          <t>£14.63</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -952,23 +952,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c97c7a05
-	0x7ff7c97c7a60
-	0x7ff7c95416ad
-	0x7ff7c959a13e
-	0x7ff7c959a44c
-	0x7ff7c95eebe7
-	0x7ff7c95eb8fb
-	0x7ff7c958b068
-	0x7ff7c958be93
-	0x7ff7c9a829a0
-	0x7ff7c9a7ce20
-	0x7ff7c9a9cc15
-	0x7ff7c97e309e
-	0x7ff7c97ead8f
-	0x7ff7c97d0be4
-	0x7ff7c97d0d9f
-	0x7ff7c97b67f8
+	0x7ff6707b7a05
+	0x7ff6707b7a60
+	0x7ff6705316ad
+	0x7ff67058a13e
+	0x7ff67058a44c
+	0x7ff6705debe7
+	0x7ff6705db8fb
+	0x7ff67057b068
+	0x7ff67057be93
+	0x7ff670a729a0
+	0x7ff670a6ce20
+	0x7ff670a8cc15
+	0x7ff6707d309e
+	0x7ff6707dad8f
+	0x7ff6707c0be4
+	0x7ff6707c0d9f
+	0x7ff6707a67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -986,7 +986,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>£21.93</t>
+          <t>£17.95</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>£18.80</t>
+          <t>£18.61</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>£18.73</t>
+          <t>£18.23</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1072,23 +1072,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c97c7a05
-	0x7ff7c97c7a60
-	0x7ff7c95416ad
-	0x7ff7c959a13e
-	0x7ff7c959a44c
-	0x7ff7c95eebe7
-	0x7ff7c95eb8fb
-	0x7ff7c958b068
-	0x7ff7c958be93
-	0x7ff7c9a829a0
-	0x7ff7c9a7ce20
-	0x7ff7c9a9cc15
-	0x7ff7c97e309e
-	0x7ff7c97ead8f
-	0x7ff7c97d0be4
-	0x7ff7c97d0d9f
-	0x7ff7c97b67f8
+	0x7ff6707b7a05
+	0x7ff6707b7a60
+	0x7ff6705316ad
+	0x7ff67058a13e
+	0x7ff67058a44c
+	0x7ff6705debe7
+	0x7ff6705db8fb
+	0x7ff67057b068
+	0x7ff67057be93
+	0x7ff670a729a0
+	0x7ff670a6ce20
+	0x7ff670a8cc15
+	0x7ff6707d309e
+	0x7ff6707dad8f
+	0x7ff6707c0be4
+	0x7ff6707c0d9f
+	0x7ff6707a67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>£20.50</t>
+          <t>£20.30</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>£20.43</t>
+          <t>£20.28</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1192,23 +1192,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c97c7a05
-	0x7ff7c97c7a60
-	0x7ff7c95416ad
-	0x7ff7c959a13e
-	0x7ff7c959a44c
-	0x7ff7c95eebe7
-	0x7ff7c95eb8fb
-	0x7ff7c958b068
-	0x7ff7c958be93
-	0x7ff7c9a829a0
-	0x7ff7c9a7ce20
-	0x7ff7c9a9cc15
-	0x7ff7c97e309e
-	0x7ff7c97ead8f
-	0x7ff7c97d0be4
-	0x7ff7c97d0d9f
-	0x7ff7c97b67f8
+	0x7ff6707b7a05
+	0x7ff6707b7a60
+	0x7ff6705316ad
+	0x7ff67058a13e
+	0x7ff67058a44c
+	0x7ff6705debe7
+	0x7ff6705db8fb
+	0x7ff67057b068
+	0x7ff67057be93
+	0x7ff670a729a0
+	0x7ff670a6ce20
+	0x7ff670a8cc15
+	0x7ff6707d309e
+	0x7ff6707dad8f
+	0x7ff6707c0be4
+	0x7ff6707c0d9f
+	0x7ff6707a67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>£20.70</t>
+          <t>£20.49</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>£20.63</t>
+          <t>£20.39</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1312,23 +1312,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c97c7a05
-	0x7ff7c97c7a60
-	0x7ff7c95416ad
-	0x7ff7c959a13e
-	0x7ff7c959a44c
-	0x7ff7c95eebe7
-	0x7ff7c95eb8fb
-	0x7ff7c958b068
-	0x7ff7c958be93
-	0x7ff7c9a829a0
-	0x7ff7c9a7ce20
-	0x7ff7c9a9cc15
-	0x7ff7c97e309e
-	0x7ff7c97ead8f
-	0x7ff7c97d0be4
-	0x7ff7c97d0d9f
-	0x7ff7c97b67f8
+	0x7ff6707b7a05
+	0x7ff6707b7a60
+	0x7ff6705316ad
+	0x7ff67058a13e
+	0x7ff67058a44c
+	0x7ff6705debe7
+	0x7ff6705db8fb
+	0x7ff67057b068
+	0x7ff67057be93
+	0x7ff670a729a0
+	0x7ff670a6ce20
+	0x7ff670a8cc15
+	0x7ff6707d309e
+	0x7ff6707dad8f
+	0x7ff6707c0be4
+	0x7ff6707c0d9f
+	0x7ff6707a67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>£23.75</t>
+          <t>£23.51</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>£23.67</t>
+          <t>£23.63</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1432,23 +1432,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c97c7a05
-	0x7ff7c97c7a60
-	0x7ff7c95416ad
-	0x7ff7c959a13e
-	0x7ff7c959a44c
-	0x7ff7c95eebe7
-	0x7ff7c95eb8fb
-	0x7ff7c958b068
-	0x7ff7c958be93
-	0x7ff7c9a829a0
-	0x7ff7c9a7ce20
-	0x7ff7c9a9cc15
-	0x7ff7c97e309e
-	0x7ff7c97ead8f
-	0x7ff7c97d0be4
-	0x7ff7c97d0d9f
-	0x7ff7c97b67f8
+	0x7ff6707b7a05
+	0x7ff6707b7a60
+	0x7ff6705316ad
+	0x7ff67058a13e
+	0x7ff67058a44c
+	0x7ff6705debe7
+	0x7ff6705db8fb
+	0x7ff67057b068
+	0x7ff67057be93
+	0x7ff670a729a0
+	0x7ff670a6ce20
+	0x7ff670a8cc15
+	0x7ff6707d309e
+	0x7ff6707dad8f
+	0x7ff6707c0be4
+	0x7ff6707c0d9f
+	0x7ff6707a67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>£25.75</t>
+          <t>£25.49</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>£25.65</t>
+          <t>£25.64</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1552,23 +1552,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c97c7a05
-	0x7ff7c97c7a60
-	0x7ff7c95416ad
-	0x7ff7c959a13e
-	0x7ff7c959a44c
-	0x7ff7c95eebe7
-	0x7ff7c95eb8fb
-	0x7ff7c958b068
-	0x7ff7c958be93
-	0x7ff7c9a829a0
-	0x7ff7c9a7ce20
-	0x7ff7c9a9cc15
-	0x7ff7c97e309e
-	0x7ff7c97ead8f
-	0x7ff7c97d0be4
-	0x7ff7c97d0d9f
-	0x7ff7c97b67f8
+	0x7ff6707b7a05
+	0x7ff6707b7a60
+	0x7ff6705316ad
+	0x7ff67058a13e
+	0x7ff67058a44c
+	0x7ff6705debe7
+	0x7ff6705db8fb
+	0x7ff67057b068
+	0x7ff67057be93
+	0x7ff670a729a0
+	0x7ff670a6ce20
+	0x7ff670a8cc15
+	0x7ff6707d309e
+	0x7ff6707dad8f
+	0x7ff6707c0be4
+	0x7ff6707c0d9f
+	0x7ff6707a67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>£25.60</t>
+          <t>£25.25</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>£25.20</t>
+          <t>£25.15</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1672,23 +1672,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c97c7a05
-	0x7ff7c97c7a60
-	0x7ff7c95416ad
-	0x7ff7c959a13e
-	0x7ff7c959a44c
-	0x7ff7c95eebe7
-	0x7ff7c95eb8fb
-	0x7ff7c958b068
-	0x7ff7c958be93
-	0x7ff7c9a829a0
-	0x7ff7c9a7ce20
-	0x7ff7c9a9cc15
-	0x7ff7c97e309e
-	0x7ff7c97ead8f
-	0x7ff7c97d0be4
-	0x7ff7c97d0d9f
-	0x7ff7c97b67f8
+	0x7ff6707b7a05
+	0x7ff6707b7a60
+	0x7ff6705316ad
+	0x7ff67058a13e
+	0x7ff67058a44c
+	0x7ff6705debe7
+	0x7ff6705db8fb
+	0x7ff67057b068
+	0x7ff67057be93
+	0x7ff670a729a0
+	0x7ff670a6ce20
+	0x7ff670a8cc15
+	0x7ff6707d309e
+	0x7ff6707dad8f
+	0x7ff6707c0be4
+	0x7ff6707c0d9f
+	0x7ff6707a67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>£33.50</t>
+          <t>£33.17</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1792,23 +1792,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c97c7a05
-	0x7ff7c97c7a60
-	0x7ff7c95416ad
-	0x7ff7c959a13e
-	0x7ff7c959a44c
-	0x7ff7c95eebe7
-	0x7ff7c95eb8fb
-	0x7ff7c958b068
-	0x7ff7c958be93
-	0x7ff7c9a829a0
-	0x7ff7c9a7ce20
-	0x7ff7c9a9cc15
-	0x7ff7c97e309e
-	0x7ff7c97ead8f
-	0x7ff7c97d0be4
-	0x7ff7c97d0d9f
-	0x7ff7c97b67f8
+	0x7ff6707b7a05
+	0x7ff6707b7a60
+	0x7ff6705316ad
+	0x7ff67058a13e
+	0x7ff67058a44c
+	0x7ff6705debe7
+	0x7ff6705db8fb
+	0x7ff67057b068
+	0x7ff67057be93
+	0x7ff670a729a0
+	0x7ff670a6ce20
+	0x7ff670a8cc15
+	0x7ff6707d309e
+	0x7ff6707dad8f
+	0x7ff6707c0be4
+	0x7ff6707c0d9f
+	0x7ff6707a67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>£31.10</t>
+          <t>£30.79</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>£30.95</t>
+          <t>£30.54</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1912,23 +1912,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c97c7a05
-	0x7ff7c97c7a60
-	0x7ff7c95416ad
-	0x7ff7c959a13e
-	0x7ff7c959a44c
-	0x7ff7c95eebe7
-	0x7ff7c95eb8fb
-	0x7ff7c958b068
-	0x7ff7c958be93
-	0x7ff7c9a829a0
-	0x7ff7c9a7ce20
-	0x7ff7c9a9cc15
-	0x7ff7c97e309e
-	0x7ff7c97ead8f
-	0x7ff7c97d0be4
-	0x7ff7c97d0d9f
-	0x7ff7c97b67f8
+	0x7ff6707b7a05
+	0x7ff6707b7a60
+	0x7ff6705316ad
+	0x7ff67058a13e
+	0x7ff67058a44c
+	0x7ff6705debe7
+	0x7ff6705db8fb
+	0x7ff67057b068
+	0x7ff67057be93
+	0x7ff670a729a0
+	0x7ff670a6ce20
+	0x7ff670a8cc15
+	0x7ff6707d309e
+	0x7ff6707dad8f
+	0x7ff6707c0be4
+	0x7ff6707c0d9f
+	0x7ff6707a67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>£39.48</t>
+          <t>£39.09</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>£38.09</t>
+          <t>£38.08</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>£37.99</t>
+          <t>£37.74</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2032,23 +2032,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c97c7a05
-	0x7ff7c97c7a60
-	0x7ff7c95416ad
-	0x7ff7c959a13e
-	0x7ff7c959a44c
-	0x7ff7c95eebe7
-	0x7ff7c95eb8fb
-	0x7ff7c958b068
-	0x7ff7c958be93
-	0x7ff7c9a829a0
-	0x7ff7c9a7ce20
-	0x7ff7c9a9cc15
-	0x7ff7c97e309e
-	0x7ff7c97ead8f
-	0x7ff7c97d0be4
-	0x7ff7c97d0d9f
-	0x7ff7c97b67f8
+	0x7ff6707b7a05
+	0x7ff6707b7a60
+	0x7ff6705316ad
+	0x7ff67058a13e
+	0x7ff67058a44c
+	0x7ff6705debe7
+	0x7ff6705db8fb
+	0x7ff67057b068
+	0x7ff67057be93
+	0x7ff670a729a0
+	0x7ff670a6ce20
+	0x7ff670a8cc15
+	0x7ff6707d309e
+	0x7ff6707dad8f
+	0x7ff6707c0be4
+	0x7ff6707c0d9f
+	0x7ff6707a67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>£38.32</t>
+          <t>£37.94</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>£38.13</t>
+          <t>£37.87</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2152,23 +2152,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c97c7a05
-	0x7ff7c97c7a60
-	0x7ff7c95416ad
-	0x7ff7c959a13e
-	0x7ff7c959a44c
-	0x7ff7c95eebe7
-	0x7ff7c95eb8fb
-	0x7ff7c958b068
-	0x7ff7c958be93
-	0x7ff7c9a829a0
-	0x7ff7c9a7ce20
-	0x7ff7c9a9cc15
-	0x7ff7c97e309e
-	0x7ff7c97ead8f
-	0x7ff7c97d0be4
-	0x7ff7c97d0d9f
-	0x7ff7c97b67f8
+	0x7ff6707b7a05
+	0x7ff6707b7a60
+	0x7ff6705316ad
+	0x7ff67058a13e
+	0x7ff67058a44c
+	0x7ff6705debe7
+	0x7ff6705db8fb
+	0x7ff67057b068
+	0x7ff67057be93
+	0x7ff670a729a0
+	0x7ff670a6ce20
+	0x7ff670a8cc15
+	0x7ff6707d309e
+	0x7ff6707dad8f
+	0x7ff6707c0be4
+	0x7ff6707c0d9f
+	0x7ff6707a67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>£38.10</t>
+          <t>£37.72</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>£37.75</t>
+          <t>£37.39</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2272,23 +2272,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c97c7a05
-	0x7ff7c97c7a60
-	0x7ff7c95416ad
-	0x7ff7c959a13e
-	0x7ff7c959a44c
-	0x7ff7c95eebe7
-	0x7ff7c95eb8fb
-	0x7ff7c958b068
-	0x7ff7c958be93
-	0x7ff7c9a829a0
-	0x7ff7c9a7ce20
-	0x7ff7c9a9cc15
-	0x7ff7c97e309e
-	0x7ff7c97ead8f
-	0x7ff7c97d0be4
-	0x7ff7c97d0d9f
-	0x7ff7c97b67f8
+	0x7ff6707b7a05
+	0x7ff6707b7a60
+	0x7ff6705316ad
+	0x7ff67058a13e
+	0x7ff67058a44c
+	0x7ff6705debe7
+	0x7ff6705db8fb
+	0x7ff67057b068
+	0x7ff67057be93
+	0x7ff670a729a0
+	0x7ff670a6ce20
+	0x7ff670a8cc15
+	0x7ff6707d309e
+	0x7ff6707dad8f
+	0x7ff6707c0be4
+	0x7ff6707c0d9f
+	0x7ff6707a67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2489,23 +2489,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c97c7a05
-	0x7ff7c97c7a60
-	0x7ff7c95416ad
-	0x7ff7c959a13e
-	0x7ff7c959a44c
-	0x7ff7c95eebe7
-	0x7ff7c95eb8fb
-	0x7ff7c958b068
-	0x7ff7c958be93
-	0x7ff7c9a829a0
-	0x7ff7c9a7ce20
-	0x7ff7c9a9cc15
-	0x7ff7c97e309e
-	0x7ff7c97ead8f
-	0x7ff7c97d0be4
-	0x7ff7c97d0d9f
-	0x7ff7c97b67f8
+	0x7ff6707b7a05
+	0x7ff6707b7a60
+	0x7ff6705316ad
+	0x7ff67058a13e
+	0x7ff67058a44c
+	0x7ff6705debe7
+	0x7ff6705db8fb
+	0x7ff67057b068
+	0x7ff67057be93
+	0x7ff670a729a0
+	0x7ff670a6ce20
+	0x7ff670a8cc15
+	0x7ff6707d309e
+	0x7ff6707dad8f
+	0x7ff6707c0be4
+	0x7ff6707c0d9f
+	0x7ff6707a67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>£28.55</t>
+          <t>£28.12</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>£28.13</t>
+          <t>£27.69</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2609,23 +2609,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c97c7a05
-	0x7ff7c97c7a60
-	0x7ff7c95416ad
-	0x7ff7c959a13e
-	0x7ff7c959a44c
-	0x7ff7c95eebe7
-	0x7ff7c95eb8fb
-	0x7ff7c958b068
-	0x7ff7c958be93
-	0x7ff7c9a829a0
-	0x7ff7c9a7ce20
-	0x7ff7c9a9cc15
-	0x7ff7c97e309e
-	0x7ff7c97ead8f
-	0x7ff7c97d0be4
-	0x7ff7c97d0d9f
-	0x7ff7c97b67f8
+	0x7ff6707b7a05
+	0x7ff6707b7a60
+	0x7ff6705316ad
+	0x7ff67058a13e
+	0x7ff67058a44c
+	0x7ff6705debe7
+	0x7ff6705db8fb
+	0x7ff67057b068
+	0x7ff67057be93
+	0x7ff670a729a0
+	0x7ff670a6ce20
+	0x7ff670a8cc15
+	0x7ff6707d309e
+	0x7ff6707dad8f
+	0x7ff6707c0be4
+	0x7ff6707c0d9f
+	0x7ff6707a67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://insulation4less.co.uk/products/celotex-pl4000-52-5mm</t>
+          <t>£33.94</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>£34.39</t>
+          <t>£33.87</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>£33.96</t>
+          <t>£33.36</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2729,23 +2729,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c97c7a05
-	0x7ff7c97c7a60
-	0x7ff7c95416ad
-	0x7ff7c959a13e
-	0x7ff7c959a44c
-	0x7ff7c95eebe7
-	0x7ff7c95eb8fb
-	0x7ff7c958b068
-	0x7ff7c958be93
-	0x7ff7c9a829a0
-	0x7ff7c9a7ce20
-	0x7ff7c9a9cc15
-	0x7ff7c97e309e
-	0x7ff7c97ead8f
-	0x7ff7c97d0be4
-	0x7ff7c97d0d9f
-	0x7ff7c97b67f8
+	0x7ff6707b7a05
+	0x7ff6707b7a60
+	0x7ff6705316ad
+	0x7ff67058a13e
+	0x7ff67058a44c
+	0x7ff6705debe7
+	0x7ff6705db8fb
+	0x7ff67057b068
+	0x7ff67057be93
+	0x7ff670a729a0
+	0x7ff670a6ce20
+	0x7ff670a8cc15
+	0x7ff6707d309e
+	0x7ff6707dad8f
+	0x7ff6707c0be4
+	0x7ff6707c0d9f
+	0x7ff6707a67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>£37.37</t>
+          <t>£36.81</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2835,12 +2835,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationuk.co.uk/products/625mm-celotex-pl4050-pir-insulated-plasterboard-2400mm-x-1200mm-625mm</t>
+          <t>£36.68</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>£36.86</t>
+          <t>£36.25</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2849,23 +2849,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c97c7a05
-	0x7ff7c97c7a60
-	0x7ff7c95416ad
-	0x7ff7c959a13e
-	0x7ff7c959a44c
-	0x7ff7c95eebe7
-	0x7ff7c95eb8fb
-	0x7ff7c958b068
-	0x7ff7c958be93
-	0x7ff7c9a829a0
-	0x7ff7c9a7ce20
-	0x7ff7c9a9cc15
-	0x7ff7c97e309e
-	0x7ff7c97ead8f
-	0x7ff7c97d0be4
-	0x7ff7c97d0d9f
-	0x7ff7c97b67f8
+	0x7ff6707b7a05
+	0x7ff6707b7a60
+	0x7ff6705316ad
+	0x7ff67058a13e
+	0x7ff67058a44c
+	0x7ff6705debe7
+	0x7ff6705db8fb
+	0x7ff67057b068
+	0x7ff67057be93
+	0x7ff670a729a0
+	0x7ff670a6ce20
+	0x7ff670a8cc15
+	0x7ff6707d309e
+	0x7ff6707dad8f
+	0x7ff6707c0be4
+	0x7ff6707c0d9f
+	0x7ff6707a67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>£42.62</t>
+          <t>£41.98</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>£42.03</t>
+          <t>£41.34</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2969,23 +2969,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c97c7a05
-	0x7ff7c97c7a60
-	0x7ff7c95416ad
-	0x7ff7c959a13e
-	0x7ff7c959a44c
-	0x7ff7c95eebe7
-	0x7ff7c95eb8fb
-	0x7ff7c958b068
-	0x7ff7c958be93
-	0x7ff7c9a829a0
-	0x7ff7c9a7ce20
-	0x7ff7c9a9cc15
-	0x7ff7c97e309e
-	0x7ff7c97ead8f
-	0x7ff7c97d0be4
-	0x7ff7c97d0d9f
-	0x7ff7c97b67f8
+	0x7ff6707b7a05
+	0x7ff6707b7a60
+	0x7ff6705316ad
+	0x7ff67058a13e
+	0x7ff67058a44c
+	0x7ff6705debe7
+	0x7ff6705db8fb
+	0x7ff67057b068
+	0x7ff67057be93
+	0x7ff670a729a0
+	0x7ff670a6ce20
+	0x7ff670a8cc15
+	0x7ff6707d309e
+	0x7ff6707dad8f
+	0x7ff6707c0be4
+	0x7ff6707c0d9f
+	0x7ff6707a67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -3089,23 +3089,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c97c7a05
-	0x7ff7c97c7a60
-	0x7ff7c95416ad
-	0x7ff7c959a13e
-	0x7ff7c959a44c
-	0x7ff7c95eebe7
-	0x7ff7c95eb8fb
-	0x7ff7c958b068
-	0x7ff7c958be93
-	0x7ff7c9a829a0
-	0x7ff7c9a7ce20
-	0x7ff7c9a9cc15
-	0x7ff7c97e309e
-	0x7ff7c97ead8f
-	0x7ff7c97d0be4
-	0x7ff7c97d0d9f
-	0x7ff7c97b67f8
+	0x7ff6707b7a05
+	0x7ff6707b7a60
+	0x7ff6705316ad
+	0x7ff67058a13e
+	0x7ff67058a44c
+	0x7ff6705debe7
+	0x7ff6705db8fb
+	0x7ff67057b068
+	0x7ff67057be93
+	0x7ff670a729a0
+	0x7ff670a6ce20
+	0x7ff670a8cc15
+	0x7ff6707d309e
+	0x7ff6707dad8f
+	0x7ff6707c0be4
+	0x7ff6707c0d9f
+	0x7ff6707a67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -3209,23 +3209,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c97c7a05
-	0x7ff7c97c7a60
-	0x7ff7c95416ad
-	0x7ff7c959a13e
-	0x7ff7c959a44c
-	0x7ff7c95eebe7
-	0x7ff7c95eb8fb
-	0x7ff7c958b068
-	0x7ff7c958be93
-	0x7ff7c9a829a0
-	0x7ff7c9a7ce20
-	0x7ff7c9a9cc15
-	0x7ff7c97e309e
-	0x7ff7c97ead8f
-	0x7ff7c97d0be4
-	0x7ff7c97d0d9f
-	0x7ff7c97b67f8
+	0x7ff6707b7a05
+	0x7ff6707b7a60
+	0x7ff6705316ad
+	0x7ff67058a13e
+	0x7ff67058a44c
+	0x7ff6705debe7
+	0x7ff6705db8fb
+	0x7ff67057b068
+	0x7ff67057be93
+	0x7ff670a729a0
+	0x7ff670a6ce20
+	0x7ff670a8cc15
+	0x7ff6707d309e
+	0x7ff6707dad8f
+	0x7ff6707c0be4
+	0x7ff6707c0d9f
+	0x7ff6707a67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -3329,23 +3329,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c97c7a05
-	0x7ff7c97c7a60
-	0x7ff7c95416ad
-	0x7ff7c959a13e
-	0x7ff7c959a44c
-	0x7ff7c95eebe7
-	0x7ff7c95eb8fb
-	0x7ff7c958b068
-	0x7ff7c958be93
-	0x7ff7c9a829a0
-	0x7ff7c9a7ce20
-	0x7ff7c9a9cc15
-	0x7ff7c97e309e
-	0x7ff7c97ead8f
-	0x7ff7c97d0be4
-	0x7ff7c97d0d9f
-	0x7ff7c97b67f8
+	0x7ff6707b7a05
+	0x7ff6707b7a60
+	0x7ff6705316ad
+	0x7ff67058a13e
+	0x7ff67058a44c
+	0x7ff6705debe7
+	0x7ff6705db8fb
+	0x7ff67057b068
+	0x7ff67057be93
+	0x7ff670a729a0
+	0x7ff670a6ce20
+	0x7ff670a8cc15
+	0x7ff6707d309e
+	0x7ff6707dad8f
+	0x7ff6707c0be4
+	0x7ff6707c0d9f
+	0x7ff6707a67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -3449,23 +3449,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c97c7a05
-	0x7ff7c97c7a60
-	0x7ff7c95416ad
-	0x7ff7c959a13e
-	0x7ff7c959a44c
-	0x7ff7c95eebe7
-	0x7ff7c95eb8fb
-	0x7ff7c958b068
-	0x7ff7c958be93
-	0x7ff7c9a829a0
-	0x7ff7c9a7ce20
-	0x7ff7c9a9cc15
-	0x7ff7c97e309e
-	0x7ff7c97ead8f
-	0x7ff7c97d0be4
-	0x7ff7c97d0d9f
-	0x7ff7c97b67f8
+	0x7ff6707b7a05
+	0x7ff6707b7a60
+	0x7ff6705316ad
+	0x7ff67058a13e
+	0x7ff67058a44c
+	0x7ff6705debe7
+	0x7ff6705db8fb
+	0x7ff67057b068
+	0x7ff67057be93
+	0x7ff670a729a0
+	0x7ff670a6ce20
+	0x7ff670a8cc15
+	0x7ff6707d309e
+	0x7ff6707dad8f
+	0x7ff6707c0be4
+	0x7ff6707c0d9f
+	0x7ff6707a67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
